--- a/Tests/Validation/Wheat/data/FAR WAA W20-01b.xlsx
+++ b/Tests/Validation/Wheat/data/FAR WAA W20-01b.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,136 +430,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z120"/>
+  <dimension ref="A1:W120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Mgmt</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population.se</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population.se</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber.se</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation.se</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
@@ -558,37 +556,25 @@
           <t>FAR WAA W20-01bMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>117.777777777778</v>
+      </c>
+      <c r="K2" t="n">
+        <v>40.0924856725971</v>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>117.777777777778</v>
-      </c>
-      <c r="N2" t="n">
-        <v>40.0924856725971</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -598,9 +584,6 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,31 +591,19 @@
           <t>FAR WAA W20-01bMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="D3" t="n">
         <v>0.3625</v>
       </c>
-      <c r="H3" t="n">
+      <c r="E3" t="n">
         <v>0.0175</v>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -648,9 +619,6 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -658,33 +626,21 @@
           <t>FAR WAA W20-01bMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>868.331444375087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.0308701067679</v>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>868.331444375087</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.0308701067679</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -698,9 +654,6 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,7 +661,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -716,27 +669,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="D5" t="n">
         <v>0.125</v>
       </c>
-      <c r="H5" t="n">
+      <c r="E5" t="n">
         <v>0.00866025403784439</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -752,9 +693,6 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -762,7 +700,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -770,29 +708,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1201.52786374033</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8224405524759471</v>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>1201.52786374033</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8224405524759471</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -806,9 +732,6 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -816,7 +739,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvIllabo</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,59 +747,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>305.368025968376</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.262177366997396</v>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>305.368025968376</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.262177366997396</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>72.788</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.688907831280788</v>
+      </c>
+      <c r="R7" t="n">
+        <v>12.675</v>
+      </c>
       <c r="S7" t="n">
-        <v>72.788</v>
+        <v>0.103077640640442</v>
       </c>
       <c r="T7" t="n">
-        <v>0.688907831280788</v>
+        <v>10.625</v>
       </c>
       <c r="U7" t="n">
-        <v>12.675</v>
+        <v>0.137689263682153</v>
       </c>
       <c r="V7" t="n">
-        <v>0.103077640640442</v>
+        <v>1.29455697666459</v>
       </c>
       <c r="W7" t="n">
-        <v>10.625</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.137689263682153</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.29455697666459</v>
-      </c>
-      <c r="Z7" t="n">
         <v>0.205126033115101</v>
       </c>
     </row>
@@ -886,37 +794,25 @@
           <t>FAR WAA W20-01bMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>92.7777777777778</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31.6276562833117</v>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>92.7777777777778</v>
-      </c>
-      <c r="N8" t="n">
-        <v>31.6276562833117</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -926,9 +822,6 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -936,31 +829,19 @@
           <t>FAR WAA W20-01bMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="D9" t="n">
         <v>0.335</v>
       </c>
-      <c r="H9" t="n">
+      <c r="E9" t="n">
         <v>0.0189296944860009</v>
       </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -976,9 +857,6 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -986,33 +864,21 @@
           <t>FAR WAA W20-01bMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>280.560460003382</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.310190406322293</v>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>280.560460003382</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.310190406322293</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1026,9 +892,6 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1036,7 +899,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1044,27 +907,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="D11" t="n">
         <v>0.1675</v>
       </c>
-      <c r="H11" t="n">
+      <c r="E11" t="n">
         <v>0.00946484724300045</v>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1080,9 +931,6 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1090,7 +938,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1098,29 +946,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>879.405104222884</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.598687050577021</v>
+      </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
-        <v>879.405104222884</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.598687050577021</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1134,9 +970,6 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1144,7 +977,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvPascal</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1152,59 +985,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>279.852963215474</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.259518696148587</v>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>279.852963215474</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.259518696148587</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>76.881</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.177220202008688</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12.8</v>
+      </c>
       <c r="S13" t="n">
-        <v>76.881</v>
+        <v>0.0816496580927728</v>
       </c>
       <c r="T13" t="n">
-        <v>0.177220202008688</v>
+        <v>11.525</v>
       </c>
       <c r="U13" t="n">
-        <v>12.8</v>
+        <v>0.110867789130417</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0816496580927728</v>
+        <v>0.712678853353214</v>
       </c>
       <c r="W13" t="n">
-        <v>11.525</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.110867789130417</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.712678853353214</v>
-      </c>
-      <c r="Z13" t="n">
         <v>0.201449297476515</v>
       </c>
     </row>
@@ -1214,37 +1032,25 @@
           <t>FAR WAA W20-01bMgmtStandardCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>87.2222222222222</v>
+      </c>
+      <c r="K14" t="n">
+        <v>37.1114992217452</v>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>87.2222222222222</v>
-      </c>
-      <c r="N14" t="n">
-        <v>37.1114992217452</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1254,9 +1060,6 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1264,31 +1067,19 @@
           <t>FAR WAA W20-01bMgmtStandardCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="D15" t="n">
         <v>0.35</v>
       </c>
-      <c r="H15" t="n">
+      <c r="E15" t="n">
         <v>0.0204124145231931</v>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1304,9 +1095,6 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1314,33 +1102,21 @@
           <t>FAR WAA W20-01bMgmtStandardCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>833.308758172298</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.22626560724893</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>833.308758172298</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.22626560724893</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1354,9 +1130,6 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1364,7 +1137,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1372,27 +1145,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="D17" t="n">
         <v>0.1525</v>
       </c>
-      <c r="H17" t="n">
+      <c r="E17" t="n">
         <v>0.008539125638299659</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1408,9 +1169,6 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1418,7 +1176,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1426,29 +1184,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>1242.313042243</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.572275499127053</v>
+      </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>1242.313042243</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.572275499127053</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1462,9 +1208,6 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1472,7 +1215,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1480,59 +1223,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>348.278176340498</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.313956948881929</v>
+      </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>348.278176340498</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.313956948881929</v>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>78.70950000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.305357031467537</v>
+      </c>
+      <c r="R19" t="n">
+        <v>12.775</v>
+      </c>
       <c r="S19" t="n">
-        <v>78.70950000000001</v>
+        <v>0.0750000000000004</v>
       </c>
       <c r="T19" t="n">
-        <v>0.305357031467537</v>
+        <v>10.15</v>
       </c>
       <c r="U19" t="n">
-        <v>12.775</v>
+        <v>0.0288675134594811</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0750000000000004</v>
+        <v>1.24498441694844</v>
       </c>
       <c r="W19" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.0288675134594811</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.24498441694844</v>
-      </c>
-      <c r="Z19" t="n">
         <v>0.169203255511106</v>
       </c>
     </row>
@@ -1542,37 +1270,25 @@
           <t>FAR WAA W20-01bMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>136.666666666667</v>
+      </c>
+      <c r="K20" t="n">
+        <v>35.1656866050315</v>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
-        <v>136.666666666667</v>
-      </c>
-      <c r="N20" t="n">
-        <v>35.1656866050315</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -1582,9 +1298,6 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1592,31 +1305,19 @@
           <t>FAR WAA W20-01bMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
+      <c r="D21" t="n">
         <v>0.3875</v>
       </c>
-      <c r="H21" t="n">
+      <c r="E21" t="n">
         <v>0.019737865470545</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1632,9 +1333,6 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1642,33 +1340,21 @@
           <t>FAR WAA W20-01bMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>346.754431488592</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.694474240640682</v>
+      </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
-        <v>346.754431488592</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.694474240640682</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -1682,9 +1368,6 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1692,7 +1375,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1700,27 +1383,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="D23" t="n">
         <v>0.1675</v>
       </c>
-      <c r="H23" t="n">
+      <c r="E23" t="n">
         <v>0.0125</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1736,9 +1407,6 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1746,7 +1414,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1754,29 +1422,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>899.828635234219</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.98220957463227</v>
+      </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>899.828635234219</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.98220957463227</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -1790,9 +1446,6 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1800,7 +1453,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvCutlass</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1808,59 +1461,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>302.093066488812</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.190325617384284</v>
+      </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>302.093066488812</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.190325617384284</v>
-      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>77.5545</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.474568137011603</v>
+      </c>
+      <c r="R25" t="n">
+        <v>12.95</v>
+      </c>
       <c r="S25" t="n">
-        <v>77.5545</v>
+        <v>0.0866025403784441</v>
       </c>
       <c r="T25" t="n">
-        <v>0.474568137011603</v>
+        <v>10.875</v>
       </c>
       <c r="U25" t="n">
-        <v>12.95</v>
+        <v>0.110867789130417</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0866025403784441</v>
+        <v>1.05955483625876</v>
       </c>
       <c r="W25" t="n">
-        <v>10.875</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.110867789130417</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.05955483625876</v>
-      </c>
-      <c r="Z25" t="n">
         <v>0.0565783802007986</v>
       </c>
     </row>
@@ -1870,37 +1508,25 @@
           <t>FAR WAA W20-01bMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>119.444444444444</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28.2460529308581</v>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>119.444444444444</v>
-      </c>
-      <c r="N26" t="n">
-        <v>28.2460529308581</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -1910,9 +1536,6 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1920,31 +1543,19 @@
           <t>FAR WAA W20-01bMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="D27" t="n">
         <v>0.415</v>
       </c>
-      <c r="H27" t="n">
+      <c r="E27" t="n">
         <v>0.015</v>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1960,9 +1571,6 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1970,33 +1578,21 @@
           <t>FAR WAA W20-01bMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>871.341250060958</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.806917986859912</v>
+      </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>871.341250060958</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.806917986859912</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2010,9 +1606,6 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2020,7 +1613,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -2028,27 +1621,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="D29" t="n">
         <v>0.17</v>
       </c>
-      <c r="H29" t="n">
+      <c r="E29" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -2064,9 +1645,6 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2074,7 +1652,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -2082,29 +1660,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>972.153228865718</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.18650943501516</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>972.153228865718</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.18650943501516</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2118,9 +1684,6 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2128,7 +1691,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvAnapurna</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -2136,59 +1699,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>298.136041057279</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.12172175345898</v>
+      </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>298.136041057279</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.12172175345898</v>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>78.74250000000001</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.604293182155814</v>
+      </c>
+      <c r="R31" t="n">
+        <v>12.9</v>
+      </c>
       <c r="S31" t="n">
-        <v>78.74250000000001</v>
+        <v>0.0408248290463862</v>
       </c>
       <c r="T31" t="n">
-        <v>0.604293182155814</v>
+        <v>11.325</v>
       </c>
       <c r="U31" t="n">
-        <v>12.9</v>
+        <v>0.438510737230762</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0408248290463862</v>
+        <v>1.7220179360226</v>
       </c>
       <c r="W31" t="n">
-        <v>11.325</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.438510737230762</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.7220179360226</v>
-      </c>
-      <c r="Z31" t="n">
         <v>0.194923612706538</v>
       </c>
     </row>
@@ -2198,37 +1746,25 @@
           <t>FAR WAA W20-01bMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>72.7777777777778</v>
+      </c>
+      <c r="K32" t="n">
+        <v>22.831913986705</v>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>72.7777777777778</v>
-      </c>
-      <c r="N32" t="n">
-        <v>22.831913986705</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -2238,9 +1774,6 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2248,31 +1781,19 @@
           <t>FAR WAA W20-01bMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+      <c r="D33" t="n">
         <v>0.4775</v>
       </c>
-      <c r="H33" t="n">
+      <c r="E33" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2288,9 +1809,6 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2298,33 +1816,21 @@
           <t>FAR WAA W20-01bMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>900.8451770856821</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.707639589557943</v>
+      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>900.8451770856821</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.707639589557943</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2338,9 +1844,6 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2348,7 +1851,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -2356,27 +1859,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="D35" t="n">
         <v>0.1775</v>
       </c>
-      <c r="H35" t="n">
+      <c r="E35" t="n">
         <v>0.0143614066163451</v>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2392,9 +1883,6 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2402,7 +1890,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -2410,29 +1898,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1182.12336894863</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.749951445385672</v>
+      </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>1182.12336894863</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.749951445385672</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2446,9 +1922,6 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2456,7 +1929,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvAccroc</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -2464,59 +1937,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>337.76389245659</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.181969844183566</v>
+      </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>337.76389245659</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.181969844183566</v>
-      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>79.6765</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.54900781718782</v>
+      </c>
+      <c r="R37" t="n">
+        <v>12.85</v>
+      </c>
       <c r="S37" t="n">
-        <v>79.6765</v>
+        <v>0.104083299973306</v>
       </c>
       <c r="T37" t="n">
-        <v>0.54900781718782</v>
+        <v>9.85</v>
       </c>
       <c r="U37" t="n">
-        <v>12.85</v>
+        <v>0.184842275106824</v>
       </c>
       <c r="V37" t="n">
-        <v>0.104083299973306</v>
+        <v>0.7124458339925041</v>
       </c>
       <c r="W37" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.184842275106824</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.7124458339925041</v>
-      </c>
-      <c r="Z37" t="n">
         <v>0.119933232153699</v>
       </c>
     </row>
@@ -2526,37 +1984,25 @@
           <t>FAR WAA W20-01bMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>107.777777777778</v>
+      </c>
+      <c r="K38" t="n">
+        <v>15.248288037214</v>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>107.777777777778</v>
-      </c>
-      <c r="N38" t="n">
-        <v>15.248288037214</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -2566,9 +2012,6 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2576,31 +2019,19 @@
           <t>FAR WAA W20-01bMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
+      <c r="D39" t="n">
         <v>0.37</v>
       </c>
-      <c r="H39" t="n">
+      <c r="E39" t="n">
         <v>0.014142135623731</v>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2616,9 +2047,6 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2626,33 +2054,21 @@
           <t>FAR WAA W20-01bMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>295.975530068713</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.471174052385552</v>
+      </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="n">
-        <v>295.975530068713</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.471174052385552</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -2666,9 +2082,6 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2676,7 +2089,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2684,27 +2097,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
+      <c r="D41" t="n">
         <v>0.175</v>
       </c>
-      <c r="H41" t="n">
+      <c r="E41" t="n">
         <v>0.0184842275106824</v>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2720,9 +2121,6 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2730,7 +2128,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2738,29 +2136,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>939.674404932803</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.701759780316987</v>
+      </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="n">
-        <v>939.674404932803</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.701759780316987</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -2774,9 +2160,6 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2784,7 +2167,7 @@
           <t>FAR WAA W20-01bMgmtStandardCvScepter</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2792,59 +2175,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>298.689779976069</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.118589267602648</v>
+      </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>298.689779976069</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.118589267602648</v>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>79.46550000000001</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.534989953176694</v>
+      </c>
+      <c r="R43" t="n">
+        <v>12.925</v>
+      </c>
       <c r="S43" t="n">
-        <v>79.46550000000001</v>
+        <v>0.110867789130417</v>
       </c>
       <c r="T43" t="n">
-        <v>0.534989953176694</v>
+        <v>10.75</v>
       </c>
       <c r="U43" t="n">
-        <v>12.925</v>
+        <v>0.0288675134594818</v>
       </c>
       <c r="V43" t="n">
-        <v>0.110867789130417</v>
+        <v>1.03953419861229</v>
       </c>
       <c r="W43" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.0288675134594818</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.03953419861229</v>
-      </c>
-      <c r="Z43" t="n">
         <v>0.0662081127138803</v>
       </c>
     </row>
@@ -2854,33 +2222,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>44042</v>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>176.666666666667</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.225622139415082</v>
+      </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>176.666666666667</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.225622139415082</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -2894,9 +2250,6 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2904,31 +2257,19 @@
           <t>FAR WAA W20-01bMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
+      <c r="D45" t="n">
         <v>0.3675</v>
       </c>
-      <c r="H45" t="n">
+      <c r="E45" t="n">
         <v>0.0175</v>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2944,9 +2285,6 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2954,33 +2292,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>910.661961884912</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.715726661069365</v>
+      </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
-        <v>910.661961884912</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.715726661069365</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -2994,9 +2320,6 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3004,7 +2327,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -3012,27 +2335,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
+      <c r="D47" t="n">
         <v>0.1425</v>
       </c>
-      <c r="H47" t="n">
+      <c r="E47" t="n">
         <v>0.0075</v>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -3048,9 +2359,6 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3058,7 +2366,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -3066,29 +2374,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>1135.31415909463</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.199630733261068</v>
+      </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="n">
-        <v>1135.31415909463</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.199630733261068</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -3102,9 +2398,6 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3112,7 +2405,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvIllabo</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -3120,59 +2413,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>273.857864734787</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.0822082545804835</v>
+      </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="n">
-        <v>273.857864734787</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.0822082545804835</v>
-      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>74.5645</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.295277694156986</v>
+      </c>
+      <c r="R49" t="n">
+        <v>12.775</v>
+      </c>
       <c r="S49" t="n">
-        <v>74.5645</v>
+        <v>0.0853912563829967</v>
       </c>
       <c r="T49" t="n">
-        <v>0.295277694156986</v>
+        <v>10.575</v>
       </c>
       <c r="U49" t="n">
-        <v>12.775</v>
+        <v>0.175</v>
       </c>
       <c r="V49" t="n">
-        <v>0.0853912563829967</v>
+        <v>1.00499744135454</v>
       </c>
       <c r="W49" t="n">
-        <v>10.575</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.00499744135454</v>
-      </c>
-      <c r="Z49" t="n">
         <v>0.137564285354153</v>
       </c>
     </row>
@@ -3182,33 +2460,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>44020</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>76.6666666666667</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.08388704928078609</v>
+      </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="n">
-        <v>76.6666666666667</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.08388704928078609</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -3222,9 +2488,6 @@
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3232,31 +2495,19 @@
           <t>FAR WAA W20-01bMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
+      <c r="D51" t="n">
         <v>0.37</v>
       </c>
-      <c r="H51" t="n">
+      <c r="E51" t="n">
         <v>0.0267706306736817</v>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -3272,9 +2523,6 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3282,33 +2530,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>239.226150604944</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.381281175871701</v>
+      </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="n">
-        <v>239.226150604944</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.381281175871701</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -3322,9 +2558,6 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3332,7 +2565,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -3340,27 +2573,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
+      <c r="D53" t="n">
         <v>0.165</v>
       </c>
-      <c r="H53" t="n">
+      <c r="E53" t="n">
         <v>0.0119023807142381</v>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3376,9 +2597,6 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3386,7 +2604,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -3394,29 +2612,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>942.258009581872</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.0373777790793</v>
+      </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="n">
-        <v>942.258009581872</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.0373777790793</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -3430,9 +2636,6 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3440,7 +2643,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvPascal</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -3448,59 +2651,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>252.563865134513</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.114644390860512</v>
+      </c>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="n">
-        <v>252.563865134513</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.114644390860512</v>
-      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>77.0745</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.943792835672462</v>
+      </c>
+      <c r="R55" t="n">
+        <v>12.725</v>
+      </c>
       <c r="S55" t="n">
-        <v>77.0745</v>
+        <v>0.0853912563829968</v>
       </c>
       <c r="T55" t="n">
-        <v>0.943792835672462</v>
+        <v>11.15</v>
       </c>
       <c r="U55" t="n">
-        <v>12.725</v>
+        <v>0.275378527364305</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0853912563829968</v>
+        <v>1.17016193159391</v>
       </c>
       <c r="W55" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0.275378527364305</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.17016193159391</v>
-      </c>
-      <c r="Z55" t="n">
         <v>0.200292625989365</v>
       </c>
     </row>
@@ -3510,33 +2698,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>44042</v>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>152.222222222222</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.274049047906458</v>
+      </c>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="n">
-        <v>152.222222222222</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.274049047906458</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3550,9 +2726,6 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3560,31 +2733,19 @@
           <t>FAR WAA W20-01bMgmtGrazedCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="D57" t="n">
         <v>0.3625</v>
       </c>
-      <c r="H57" t="n">
+      <c r="E57" t="n">
         <v>0.0047871355387817</v>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3600,9 +2761,6 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3610,33 +2768,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>888.4160467296859</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.287423077603576</v>
+      </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="n">
-        <v>888.4160467296859</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.287423077603576</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -3650,9 +2796,6 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3660,7 +2803,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -3668,27 +2811,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
+      <c r="D59" t="n">
         <v>0.1825</v>
       </c>
-      <c r="H59" t="n">
+      <c r="E59" t="n">
         <v>0.0131497781983829</v>
       </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3704,9 +2835,6 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3714,7 +2842,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -3722,29 +2850,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>959.585942973238</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.157500308208242</v>
+      </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="n">
-        <v>959.585942973238</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.157500308208242</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
@@ -3758,9 +2874,6 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3768,7 +2881,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -3776,59 +2889,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>329.254044798724</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.118802678430637</v>
+      </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="n">
-        <v>329.254044798724</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.118802678430637</v>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>80.117</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.451905963669435</v>
+      </c>
+      <c r="R61" t="n">
+        <v>12.8</v>
+      </c>
       <c r="S61" t="n">
-        <v>80.117</v>
+        <v>0.12909944487358</v>
       </c>
       <c r="T61" t="n">
-        <v>0.451905963669435</v>
+        <v>9.9</v>
       </c>
       <c r="U61" t="n">
-        <v>12.8</v>
+        <v>0.108012344973465</v>
       </c>
       <c r="V61" t="n">
-        <v>0.12909944487358</v>
+        <v>1.0173377880657</v>
       </c>
       <c r="W61" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0.108012344973465</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.0173377880657</v>
-      </c>
-      <c r="Z61" t="n">
         <v>0.164891946293569</v>
       </c>
     </row>
@@ -3838,33 +2936,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>44020</v>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>90.5555555555556</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.181074752087698</v>
+      </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>90.5555555555556</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.181074752087698</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -3878,9 +2964,6 @@
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3888,31 +2971,19 @@
           <t>FAR WAA W20-01bMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
+      <c r="D63" t="n">
         <v>0.3825</v>
       </c>
-      <c r="H63" t="n">
+      <c r="E63" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3928,9 +2999,6 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3938,33 +3006,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>328.650424009841</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.820185099729282</v>
+      </c>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="n">
-        <v>328.650424009841</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.820185099729282</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -3978,9 +3034,6 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3988,7 +3041,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -3996,27 +3049,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
+      <c r="D65" t="n">
         <v>0.175</v>
       </c>
-      <c r="H65" t="n">
+      <c r="E65" t="n">
         <v>0.00645497224367903</v>
       </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -4032,9 +3073,6 @@
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4042,7 +3080,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -4050,29 +3088,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>973.679847713904</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.07729173651791</v>
+      </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="n">
-        <v>973.679847713904</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1.07729173651791</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -4086,9 +3112,6 @@
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4096,7 +3119,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvCutlass</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -4104,59 +3127,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>298.67659353848</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.223681300448993</v>
+      </c>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="n">
-        <v>298.67659353848</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0.223681300448993</v>
-      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>78.3065</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.63090589631101</v>
+      </c>
+      <c r="R67" t="n">
+        <v>12.85</v>
+      </c>
       <c r="S67" t="n">
-        <v>78.3065</v>
+        <v>0.0645497224367904</v>
       </c>
       <c r="T67" t="n">
-        <v>0.63090589631101</v>
+        <v>10.825</v>
       </c>
       <c r="U67" t="n">
-        <v>12.85</v>
+        <v>0.149303940559741</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0645497224367904</v>
+        <v>0.859478579160794</v>
       </c>
       <c r="W67" t="n">
-        <v>10.825</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0.149303940559741</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0.859478579160794</v>
-      </c>
-      <c r="Z67" t="n">
         <v>0.148295402028738</v>
       </c>
     </row>
@@ -4166,33 +3174,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>44042</v>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>226.666666666667</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0551839423175976</v>
+      </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="n">
-        <v>226.666666666667</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.0551839423175976</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -4206,9 +3202,6 @@
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4216,31 +3209,19 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
+      <c r="D69" t="n">
         <v>0.4275</v>
       </c>
-      <c r="H69" t="n">
+      <c r="E69" t="n">
         <v>0.0165201896679992</v>
       </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -4256,9 +3237,6 @@
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4266,33 +3244,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>766.443943783221</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.844835991649036</v>
+      </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="n">
-        <v>766.443943783221</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.844835991649036</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -4306,9 +3272,6 @@
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4316,7 +3279,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -4324,27 +3287,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
+      <c r="D71" t="n">
         <v>0.1725</v>
       </c>
-      <c r="H71" t="n">
+      <c r="E71" t="n">
         <v>0.00946484724300046</v>
       </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -4360,9 +3311,6 @@
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4370,7 +3318,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -4378,29 +3326,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>1087.19727718005</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.45438014645234</v>
+      </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="n">
-        <v>1087.19727718005</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1.45438014645234</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -4414,9 +3350,6 @@
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4424,7 +3357,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAnapurna</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -4432,59 +3365,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>293.106570570695</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.137990205403933</v>
+      </c>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="n">
-        <v>293.106570570695</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0.137990205403933</v>
-      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>80.441</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.487741393226642</v>
+      </c>
+      <c r="R73" t="n">
+        <v>12.975</v>
+      </c>
       <c r="S73" t="n">
-        <v>80.441</v>
+        <v>0.0478713553878169</v>
       </c>
       <c r="T73" t="n">
-        <v>0.487741393226642</v>
+        <v>10.775</v>
       </c>
       <c r="U73" t="n">
-        <v>12.975</v>
+        <v>0.179698822107065</v>
       </c>
       <c r="V73" t="n">
-        <v>0.0478713553878169</v>
+        <v>1.41396330615809</v>
       </c>
       <c r="W73" t="n">
-        <v>10.775</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0.179698822107065</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1.41396330615809</v>
-      </c>
-      <c r="Z73" t="n">
         <v>0.167266380592081</v>
       </c>
     </row>
@@ -4494,33 +3412,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>44042</v>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>201.666666666667</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0611111111111111</v>
+      </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="n">
-        <v>201.666666666667</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.0611111111111111</v>
-      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -4534,9 +3440,6 @@
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4544,31 +3447,19 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
+      <c r="D75" t="n">
         <v>0.47</v>
       </c>
-      <c r="H75" t="n">
+      <c r="E75" t="n">
         <v>0.0248327740429189</v>
       </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4584,9 +3475,6 @@
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4594,33 +3482,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>896.357505352527</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.398167696517466</v>
+      </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="n">
-        <v>896.357505352527</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.398167696517466</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -4634,9 +3510,6 @@
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4644,7 +3517,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -4652,27 +3525,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
+      <c r="D77" t="n">
         <v>0.18</v>
       </c>
-      <c r="H77" t="n">
+      <c r="E77" t="n">
         <v>0.0108012344973464</v>
       </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4688,9 +3549,6 @@
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4698,7 +3556,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -4706,29 +3564,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>1144.97503327165</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.048150259461878</v>
+      </c>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="n">
-        <v>1144.97503327165</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.048150259461878</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -4742,9 +3588,6 @@
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4752,7 +3595,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvAccroc</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -4760,59 +3603,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>323.579082899719</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.229705322420685</v>
+      </c>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="n">
-        <v>323.579082899719</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.229705322420685</v>
-      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>80.0655</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.527627630689168</v>
+      </c>
+      <c r="R79" t="n">
+        <v>12.925</v>
+      </c>
       <c r="S79" t="n">
-        <v>80.0655</v>
+        <v>0.0853912563829967</v>
       </c>
       <c r="T79" t="n">
-        <v>0.527627630689168</v>
+        <v>10.075</v>
       </c>
       <c r="U79" t="n">
-        <v>12.925</v>
+        <v>0.370528901256928</v>
       </c>
       <c r="V79" t="n">
-        <v>0.0853912563829967</v>
+        <v>0.892301373474385</v>
       </c>
       <c r="W79" t="n">
-        <v>10.075</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0.370528901256928</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0.892301373474385</v>
-      </c>
-      <c r="Z79" t="n">
         <v>0.0465723800703864</v>
       </c>
     </row>
@@ -4822,33 +3650,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="3" t="n">
         <v>44020</v>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>75</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.154327160370375</v>
+      </c>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="n">
-        <v>75</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.154327160370375</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -4862,9 +3678,6 @@
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4872,31 +3685,19 @@
           <t>FAR WAA W20-01bMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
+      <c r="D81" t="n">
         <v>0.36</v>
       </c>
-      <c r="H81" t="n">
+      <c r="E81" t="n">
         <v>0.0108012344973464</v>
       </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4912,9 +3713,6 @@
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4922,33 +3720,21 @@
           <t>FAR WAA W20-01bMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>238.981082425049</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.419500226173362</v>
+      </c>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="n">
-        <v>238.981082425049</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0.419500226173362</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
@@ -4962,9 +3748,6 @@
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4972,7 +3755,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -4980,27 +3763,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
+      <c r="D83" t="n">
         <v>0.175</v>
       </c>
-      <c r="H83" t="n">
+      <c r="E83" t="n">
         <v>0.0184842275106824</v>
       </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -5016,9 +3787,6 @@
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5026,7 +3794,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -5034,29 +3802,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>754.586345503513</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.845695023044491</v>
+      </c>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="n">
-        <v>754.586345503513</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0.845695023044491</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
@@ -5070,9 +3826,6 @@
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5080,7 +3833,7 @@
           <t>FAR WAA W20-01bMgmtGrazedCvScepter</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -5088,59 +3841,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>288.924000180734</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.13784198855209</v>
+      </c>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="n">
-        <v>288.924000180734</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0.13784198855209</v>
-      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
+      <c r="P85" t="n">
+        <v>80.179</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.545701688959578</v>
+      </c>
+      <c r="R85" t="n">
+        <v>12.975</v>
+      </c>
       <c r="S85" t="n">
-        <v>80.179</v>
+        <v>0.0629152869605894</v>
       </c>
       <c r="T85" t="n">
-        <v>0.545701688959578</v>
+        <v>10.65</v>
       </c>
       <c r="U85" t="n">
-        <v>12.975</v>
+        <v>0.15545631755148</v>
       </c>
       <c r="V85" t="n">
-        <v>0.0629152869605894</v>
+        <v>1.19021786788898</v>
       </c>
       <c r="W85" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0.15545631755148</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>1.19021786788898</v>
-      </c>
-      <c r="Z85" t="n">
         <v>0.117497903402281</v>
       </c>
     </row>
@@ -5150,31 +3888,19 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
+      <c r="D86" t="n">
         <v>0.365</v>
       </c>
-      <c r="H86" t="n">
+      <c r="E86" t="n">
         <v>0.0104083299973307</v>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -5190,9 +3916,6 @@
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5200,33 +3923,21 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>986.645696279088</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1.23777037068072</v>
+      </c>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="n">
-        <v>986.645696279088</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1.23777037068072</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
@@ -5240,9 +3951,6 @@
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5250,7 +3958,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -5258,27 +3966,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+      <c r="D88" t="n">
         <v>0.13</v>
       </c>
-      <c r="H88" t="n">
+      <c r="E88" t="n">
         <v>0.0129099444873581</v>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -5294,9 +3990,6 @@
       <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5304,7 +3997,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -5312,29 +4005,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>1062.07769156521</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1.85595583660371</v>
+      </c>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="n">
-        <v>1062.07769156521</v>
-      </c>
-      <c r="J89" t="n">
-        <v>1.85595583660371</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
@@ -5348,9 +4029,6 @@
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5358,7 +4036,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvIllabo</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -5366,59 +4044,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>303.494596765975</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.09640249119423611</v>
+      </c>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="n">
-        <v>303.494596765975</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0.09640249119423611</v>
-      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>73.0675</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.697964361554369</v>
+      </c>
+      <c r="R90" t="n">
+        <v>12.725</v>
+      </c>
       <c r="S90" t="n">
-        <v>73.0675</v>
+        <v>0.125</v>
       </c>
       <c r="T90" t="n">
-        <v>0.697964361554369</v>
+        <v>11.7</v>
       </c>
       <c r="U90" t="n">
-        <v>12.725</v>
+        <v>0.158113883008419</v>
       </c>
       <c r="V90" t="n">
-        <v>0.125</v>
+        <v>1.46542154697102</v>
       </c>
       <c r="W90" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0.158113883008419</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>1.46542154697102</v>
-      </c>
-      <c r="Z90" t="n">
         <v>0.0943487640986716</v>
       </c>
     </row>
@@ -5428,31 +4091,19 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
+      <c r="D91" t="n">
         <v>0.35</v>
       </c>
-      <c r="H91" t="n">
+      <c r="E91" t="n">
         <v>0.0273861278752583</v>
       </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -5468,9 +4119,6 @@
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5478,33 +4126,21 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>377.881779822088</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.568977449070817</v>
+      </c>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="n">
-        <v>377.881779822088</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0.568977449070817</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
@@ -5518,9 +4154,6 @@
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5528,7 +4161,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -5536,27 +4169,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
+      <c r="D93" t="n">
         <v>0.145</v>
       </c>
-      <c r="H93" t="n">
+      <c r="E93" t="n">
         <v>0.00866025403784438</v>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5572,9 +4193,6 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5582,7 +4200,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -5590,29 +4208,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>994.845584698526</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.416821674472257</v>
+      </c>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="n">
-        <v>994.845584698526</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0.416821674472257</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
@@ -5626,9 +4232,6 @@
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5636,7 +4239,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvPascal</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -5644,59 +4247,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Pascal</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>276.766047313175</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.226742779928372</v>
+      </c>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="n">
-        <v>276.766047313175</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0.226742779928372</v>
-      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
+      <c r="P95" t="n">
+        <v>76.137</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.669515496459941</v>
+      </c>
+      <c r="R95" t="n">
+        <v>12.625</v>
+      </c>
       <c r="S95" t="n">
-        <v>76.137</v>
+        <v>0.07500000000000009</v>
       </c>
       <c r="T95" t="n">
-        <v>0.669515496459941</v>
+        <v>11.825</v>
       </c>
       <c r="U95" t="n">
-        <v>12.625</v>
+        <v>0.0750000000000004</v>
       </c>
       <c r="V95" t="n">
-        <v>0.07500000000000009</v>
+        <v>0.954793840727225</v>
       </c>
       <c r="W95" t="n">
-        <v>11.825</v>
-      </c>
-      <c r="X95" t="n">
-        <v>0.0750000000000004</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>0.954793840727225</v>
-      </c>
-      <c r="Z95" t="n">
         <v>0.0929679147919323</v>
       </c>
     </row>
@@ -5706,31 +4294,19 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
+      <c r="D96" t="n">
         <v>0.325</v>
       </c>
-      <c r="H96" t="n">
+      <c r="E96" t="n">
         <v>0.0262995563967658</v>
       </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5746,9 +4322,6 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5756,33 +4329,21 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>926.355886508854</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.493479466128449</v>
+      </c>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="n">
-        <v>926.355886508854</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0.493479466128449</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
@@ -5796,9 +4357,6 @@
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5806,7 +4364,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -5814,27 +4372,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
+      <c r="D98" t="n">
         <v>0.135</v>
       </c>
-      <c r="H98" t="n">
+      <c r="E98" t="n">
         <v>0.0104083299973307</v>
       </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5850,9 +4396,6 @@
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5860,7 +4403,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -5868,29 +4411,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>1054.39959606548</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1.0323441361849</v>
+      </c>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="n">
-        <v>1054.39959606548</v>
-      </c>
-      <c r="J99" t="n">
-        <v>1.0323441361849</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
@@ -5904,9 +4435,6 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5914,7 +4442,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvLRPB TBC</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -5922,59 +4450,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>LRPB TBC</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>339.149823404648</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.19572474818939</v>
+      </c>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="n">
-        <v>339.149823404648</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.19572474818939</v>
-      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>76.83799999999999</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1.07588506201484</v>
+      </c>
+      <c r="R100" t="n">
+        <v>12.7</v>
+      </c>
       <c r="S100" t="n">
-        <v>76.83799999999999</v>
+        <v>0.129099444873581</v>
       </c>
       <c r="T100" t="n">
-        <v>1.07588506201484</v>
+        <v>11.35</v>
       </c>
       <c r="U100" t="n">
-        <v>12.7</v>
+        <v>0.239791576165636</v>
       </c>
       <c r="V100" t="n">
-        <v>0.129099444873581</v>
+        <v>1.49407768978892</v>
       </c>
       <c r="W100" t="n">
-        <v>11.35</v>
-      </c>
-      <c r="X100" t="n">
-        <v>0.239791576165636</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>1.49407768978892</v>
-      </c>
-      <c r="Z100" t="n">
         <v>0.287925494096301</v>
       </c>
     </row>
@@ -5984,31 +4497,19 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
+      <c r="D101" t="n">
         <v>0.3525</v>
       </c>
-      <c r="H101" t="n">
+      <c r="E101" t="n">
         <v>0.0225</v>
       </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -6024,9 +4525,6 @@
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6034,33 +4532,21 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>375.02793502289</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.692803108151368</v>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="n">
-        <v>375.02793502289</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0.692803108151368</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
@@ -6074,9 +4560,6 @@
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6084,7 +4567,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -6092,27 +4575,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
+      <c r="D103" t="n">
         <v>0.1725</v>
       </c>
-      <c r="H103" t="n">
+      <c r="E103" t="n">
         <v>0.0205649377987551</v>
       </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -6128,9 +4599,6 @@
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6138,7 +4606,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -6146,29 +4614,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="n">
+        <v>1002.60023402172</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.967871201860548</v>
+      </c>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="n">
-        <v>1002.60023402172</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0.967871201860548</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
@@ -6182,9 +4638,6 @@
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6192,7 +4645,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvCutlass</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -6200,59 +4653,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Cutlass</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>306.3392244349</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.182760471096813</v>
+      </c>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="n">
-        <v>306.3392244349</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0.182760471096813</v>
-      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
+      <c r="P105" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.706539453958519</v>
+      </c>
+      <c r="R105" t="n">
+        <v>12.9</v>
+      </c>
       <c r="S105" t="n">
-        <v>76.15000000000001</v>
+        <v>0.091287092917528</v>
       </c>
       <c r="T105" t="n">
-        <v>0.706539453958519</v>
+        <v>11.15</v>
       </c>
       <c r="U105" t="n">
-        <v>12.9</v>
+        <v>0.170782512765993</v>
       </c>
       <c r="V105" t="n">
-        <v>0.091287092917528</v>
+        <v>1.25729716682464</v>
       </c>
       <c r="W105" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="X105" t="n">
-        <v>0.170782512765993</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>1.25729716682464</v>
-      </c>
-      <c r="Z105" t="n">
         <v>0.11690020014089</v>
       </c>
     </row>
@@ -6262,31 +4700,19 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
+      <c r="D106" t="n">
         <v>0.4675</v>
       </c>
-      <c r="H106" t="n">
+      <c r="E106" t="n">
         <v>0.0252899848424892</v>
       </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -6302,9 +4728,6 @@
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6312,33 +4735,21 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>1044.31418447215</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.121362963276</v>
+      </c>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="n">
-        <v>1044.31418447215</v>
-      </c>
-      <c r="J107" t="n">
-        <v>1.121362963276</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
@@ -6352,9 +4763,6 @@
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6362,7 +4770,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -6370,27 +4778,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
+      <c r="D108" t="n">
         <v>0.175</v>
       </c>
-      <c r="H108" t="n">
+      <c r="E108" t="n">
         <v>0.013228756555323</v>
       </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -6406,9 +4802,6 @@
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6416,7 +4809,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -6424,29 +4817,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>1081.37621631936</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.68710411618628</v>
+      </c>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="n">
-        <v>1081.37621631936</v>
-      </c>
-      <c r="J109" t="n">
-        <v>1.68710411618628</v>
-      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
@@ -6460,9 +4841,6 @@
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6470,7 +4848,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAnapurna</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -6478,59 +4856,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>304.574164070258</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.291529345363631</v>
+      </c>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="n">
-        <v>304.574164070258</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0.291529345363631</v>
-      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>78.486</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.562331456230816</v>
+      </c>
+      <c r="R110" t="n">
+        <v>12.825</v>
+      </c>
       <c r="S110" t="n">
-        <v>78.486</v>
+        <v>0.047871355387817</v>
       </c>
       <c r="T110" t="n">
-        <v>0.562331456230816</v>
+        <v>12.7</v>
       </c>
       <c r="U110" t="n">
-        <v>12.825</v>
+        <v>0.402077936060494</v>
       </c>
       <c r="V110" t="n">
-        <v>0.047871355387817</v>
+        <v>1.4951475116305</v>
       </c>
       <c r="W110" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="X110" t="n">
-        <v>0.402077936060494</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1.4951475116305</v>
-      </c>
-      <c r="Z110" t="n">
         <v>0.188619785435824</v>
       </c>
     </row>
@@ -6540,31 +4903,19 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
+      <c r="D111" t="n">
         <v>0.525</v>
       </c>
-      <c r="H111" t="n">
+      <c r="E111" t="n">
         <v>0.0217944947177034</v>
       </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -6580,9 +4931,6 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
-      <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6590,33 +4938,21 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>950.852856460608</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.997317022287585</v>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="n">
-        <v>950.852856460608</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0.997317022287585</v>
-      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
@@ -6630,9 +4966,6 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6640,7 +4973,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -6648,27 +4981,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
+      <c r="D113" t="n">
         <v>0.1575</v>
       </c>
-      <c r="H113" t="n">
+      <c r="E113" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6684,9 +5005,6 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
-      <c r="Y113" t="inlineStr"/>
-      <c r="Z113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6694,7 +5012,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -6702,29 +5020,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>1023.69508878</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.06285723527865</v>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="n">
-        <v>1023.69508878</v>
-      </c>
-      <c r="J114" t="n">
-        <v>1.06285723527865</v>
-      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
@@ -6738,9 +5044,6 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6748,7 +5051,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvAccroc</t>
         </is>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -6756,59 +5059,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>328.022391157799</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.26286246800151</v>
+      </c>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="n">
-        <v>328.022391157799</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0.26286246800151</v>
-      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>80.593</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.460372675123099</v>
+      </c>
+      <c r="R115" t="n">
+        <v>13.025</v>
+      </c>
       <c r="S115" t="n">
-        <v>80.593</v>
+        <v>0.149303940559741</v>
       </c>
       <c r="T115" t="n">
-        <v>0.460372675123099</v>
+        <v>11.3</v>
       </c>
       <c r="U115" t="n">
-        <v>13.025</v>
+        <v>0.241522945769824</v>
       </c>
       <c r="V115" t="n">
-        <v>0.149303940559741</v>
+        <v>0.504909570869017</v>
       </c>
       <c r="W115" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0.241522945769824</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0.504909570869017</v>
-      </c>
-      <c r="Z115" t="n">
         <v>0.0295612135569362</v>
       </c>
     </row>
@@ -6818,31 +5106,19 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
+      <c r="D116" t="n">
         <v>0.375</v>
       </c>
-      <c r="H116" t="n">
+      <c r="E116" t="n">
         <v>0.0132287565553229</v>
       </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -6858,9 +5134,6 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
-      <c r="Y116" t="inlineStr"/>
-      <c r="Z116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6868,33 +5141,21 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="3" t="n">
         <v>44132</v>
       </c>
       <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>347.44557188334</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.623287689121991</v>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="n">
-        <v>347.44557188334</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0.623287689121991</v>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
@@ -6908,9 +5169,6 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6918,7 +5176,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="3" t="n">
         <v>44161</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -6926,27 +5184,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
+      <c r="D118" t="n">
         <v>0.1675</v>
       </c>
-      <c r="H118" t="n">
+      <c r="E118" t="n">
         <v>0.0125</v>
       </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -6962,9 +5208,6 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
-      <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6972,7 +5215,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -6980,29 +5223,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>1057.25512672751</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.235217187485577</v>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="n">
-        <v>1057.25512672751</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0.235217187485577</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
@@ -7016,9 +5247,6 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7026,7 +5254,7 @@
           <t>FAR WAA W20-01bMgmtHigh InputCvScepter</t>
         </is>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="3" t="n">
         <v>44182</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -7034,59 +5262,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>High Input</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>306.400439773383</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.158851500134202</v>
+      </c>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="n">
-        <v>306.400439773383</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0.158851500134202</v>
-      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
+      <c r="P120" t="n">
+        <v>79.41500000000001</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.532040411998941</v>
+      </c>
+      <c r="R120" t="n">
+        <v>12.875</v>
+      </c>
       <c r="S120" t="n">
-        <v>79.41500000000001</v>
+        <v>0.07500000000000009</v>
       </c>
       <c r="T120" t="n">
-        <v>0.532040411998941</v>
+        <v>11.25</v>
       </c>
       <c r="U120" t="n">
-        <v>12.875</v>
+        <v>0.306865877325366</v>
       </c>
       <c r="V120" t="n">
-        <v>0.07500000000000009</v>
+        <v>0.8893169997332701</v>
       </c>
       <c r="W120" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="X120" t="n">
-        <v>0.306865877325366</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>0.8893169997332701</v>
-      </c>
-      <c r="Z120" t="n">
         <v>0.08563340452106979</v>
       </c>
     </row>
